--- a/exports/colleges/8164_welcomgroup-graduate-school-of-hotel-administration-wgsha-manipal.xlsx
+++ b/exports/colleges/8164_welcomgroup-graduate-school-of-hotel-administration-wgsha-manipal.xlsx
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
     <col width="53" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>Bachelor of Hotel Management [BHM]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bachelor of Hotel Management [BHM]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.1 Lakhs</t>
+          <t>21.1 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with 45%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 26 Apr 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>Master of Hotel Management [MHM]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Master of Hotel Management [MHM]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.1 Lakhs</t>
+          <t>7.1 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation with 50%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 26 Apr 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.67 Lakhs</t>
+          <t>18.67 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10+2</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 15 May 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.34 Lakhs</t>
+          <t>6.34 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 50%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 26 Apr 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -945,22 +945,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>Bachelor of Hotel Management [BHM]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>Bachelor of Hotel Management [BHM]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>₹ 18.67 Lakhs - 21.1 Lakhs</t>
+          <t>21.1 Lakhs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Master of Hotel Management [MHM]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Master of Hotel Management [MHM]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>₹ 18.67 Lakhs - 21.1 Lakhs</t>
+          <t>7.1 Lakhs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10+2</t>
+          <t>Graduation with 50%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>₹ 7.1 Lakhs</t>
+          <t>18.67 Lakhs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Graduation with 50%</t>
+          <t>10+2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Science [M.Sc] (Nutrition and Dietetics)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Science [M.Sc] (Nutrition and Dietetics)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>₹ 6.34 Lakhs</t>
+          <t>6.34 Lakhs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 45%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>₹ 16.13 Lakhs - 18.67 Lakhs</t>
+          <t>₹ 7.1 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>₹18.67 Lakhs</t>
+          <t>₹ 6.34 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,379 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>₹ 7.1 Lakhs</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>₹ 7.1 Lakhs</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>M.Sc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fee Type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fee Type</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Amount (INR)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>IIT JAM</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>M.Sc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>₹ 6.34 Lakhs</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>IIT JAM</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>M.Sc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>₹ 6.34 Lakhs</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>IIT JAM</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>8164</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>M.Sc</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Fees (2026 - 2027)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fees (2026 - 2027)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Total Fees</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IIT JAM</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
